--- a/Doc/ฟอร์มเอกสารแบบ-บ1_67130701930 DBIS.xlsx
+++ b/Doc/ฟอร์มเอกสารแบบ-บ1_67130701930 DBIS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krissanap/Document/KMUTT/Short Paper/Codesk_v2/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF1959D6-DE84-BC4E-AC31-71561648AA1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5DED67-6715-CA44-8E05-29985FE01F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -370,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="148">
   <si>
     <t>มหาวิทยาลัยเทคโนโลยีพระจอมเกล้าธนบุรี</t>
   </si>
@@ -949,7 +949,7 @@
   <numFmts count="1">
     <numFmt numFmtId="187" formatCode="[$-107041E]d\ mmmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1000,13 +1000,6 @@
       <b/>
       <u/>
       <sz val="14"/>
-      <name val="Angsana New"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="14"/>
-      <color theme="1"/>
       <name val="Angsana New"/>
       <family val="1"/>
     </font>
@@ -1101,7 +1094,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1152,6 +1145,15 @@
       <right/>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1214,26 +1216,25 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1244,6 +1245,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1807,361 +1809,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1072558</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>174313</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>706550</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>149412</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="TextBox 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000017000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1439248" y="4986003"/>
-          <a:ext cx="6028710" cy="225522"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400">
-              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>เพื่อพัฒนาระบบบริหารการจองพื้นที่และการเข้าใช้สำนักงาน ให้สามารถจัดการข้อมูลการจอง พนักงาน แผนก และสิทธิ์การ</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1400">
-            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1068791</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>172321</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>585693</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>172321</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="TextBox 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000018000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1437340" y="5257301"/>
-          <a:ext cx="5906745" cy="254000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400">
-              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>ใช้งานได้อย่างเป็นระบบเพื่อช่วยลดความซ้ำซ้อนและข้อผิดพลาดในการบริหารพื้นที่สำนักงาน พร้อมสนับสนุนการ</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1400">
-            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1071779</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>170329</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>588681</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>170329</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="TextBox 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000019000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1440328" y="5509309"/>
-          <a:ext cx="5906745" cy="254000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400">
-              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>ตรวจสอบสถานะและประวัติการใช้งานได้อย่างชัดเจน</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1400">
-            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>323655</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>33421</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>9550</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>84912</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="TextBox 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="691287" y="8288421"/>
-          <a:ext cx="6074090" cy="228145"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400">
-              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>ศึกษาความต้องการของผู้ใช้งาน วิเคราะห์และออกแบบระบบ จากนั้นพัฒนาและทดสอบการทำงานตามขอบเขตที่กำหนด</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1400">
-            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>319887</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>136467</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>457466</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>184211</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="TextBox 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00001C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="687519" y="8568121"/>
-          <a:ext cx="5905097" cy="253045"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="th-TH" sz="1400">
-              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>พร้อมประเมินผลการใช้งาน เพื่อสรุปประสิทธิภาพและความเหมาะสมของระบบที่พัฒนาขึ้น</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1400">
-            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>420151</xdr:colOff>
       <xdr:row>34</xdr:row>
@@ -2216,11 +1863,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
+            <a:rPr lang="th-TH" sz="1400">
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
             <a:rPr lang="en-US" sz="1400">
               <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
               <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
             </a:rPr>
-            <a:t>10</a:t>
+            <a:t>4</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1400" baseline="0">
@@ -2250,6 +1904,532 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>268309</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>107324</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>580260</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>158815</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="634999" y="8326549"/>
+          <a:ext cx="6080613" cy="230365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400">
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>ศึกษาและวิเคราะห์ความต้องการ ออกแบบกระบวนการทำงาน ฐานข้อมูล และสิทธิ์ของผู้ใช้งาน โดยใช้ Supabase PostgreSQL </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>250423</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>205703</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>562374</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>230364</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="TextBox 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-00000D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="617113" y="8603802"/>
+          <a:ext cx="6080613" cy="301914"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400">
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>ในการสร้างฐานข้อมูล พัฒนาระบบหลังบ้านด้วยภาษา C# บน ASP.NET Core และพัฒนาส่วนติดต่อผู้ใช้งานด้วยภาษา </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>277253</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>205705</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>589204</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>248252</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="TextBox 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000010000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="643943" y="8881057"/>
+          <a:ext cx="6080613" cy="319801"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400">
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>TypeScript โดยใช้ React จากนั้นทดสอบและปรับปรุงการทำงานของระบบให้ถูกต้องตามวัตถุประสงค์ของโครงการ</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400">
+            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1082184</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>178874</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>716176</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>153973</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000012000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1448874" y="4990564"/>
+          <a:ext cx="6028710" cy="225522"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400">
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>1. เพื่อพัฒนาเว็บแอปพลิเคชันสำหรับบริหารจัดการการจองที่นั่งเข้าออฟฟิศให้มีความสะดวกและเป็นระบบ </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1073240</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>205703</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>707232</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>180803</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000013000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1439930" y="5267816"/>
+          <a:ext cx="6028710" cy="252353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400">
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>2. เพื่อพัฒนาแอปพลิเคชันสำหรับระบบจองที่นั่ง  </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1073240</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>205704</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>707232</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>180803</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1439930" y="5545070"/>
+          <a:ext cx="6028710" cy="252353"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:r>
+            <a:rPr lang="th-TH" sz="1400">
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>3. เพื่อสนับสนุนการติดตาม ตรวจสอบ และบริหารจัดการข้อมูลการจองที่นั่งของผู้ใช้งาน</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>268992</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>225522</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000015000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10455141" y="6314225"/>
+          <a:ext cx="6028710" cy="225522"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr lvl="0"/>
+          <a:endParaRPr lang="th-TH" sz="1400">
+            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>733377</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>240963</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>376703</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>34700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="รูปภาพ 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2BC5E7B-B042-7DBB-2F9A-423584C1D0F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3747391" y="9944836"/>
+          <a:ext cx="3390720" cy="1493033"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -2555,642 +2735,642 @@
   <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="22" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="28"/>
-    <col min="2" max="2" width="26.83203125" style="28" customWidth="1"/>
-    <col min="3" max="3" width="33.83203125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="40.1640625" style="28" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="19" style="28" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" style="28" customWidth="1"/>
-    <col min="8" max="16384" width="8.83203125" style="28"/>
+    <col min="1" max="1" width="8.83203125" style="27"/>
+    <col min="2" max="2" width="26.83203125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="33.83203125" style="27" customWidth="1"/>
+    <col min="4" max="4" width="40.1640625" style="27" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" style="27" customWidth="1"/>
+    <col min="6" max="6" width="19" style="27" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" style="27" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="27"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="27" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="28">
+      <c r="A3" s="27">
         <v>1</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="28">
+      <c r="A4" s="27">
         <v>2</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="27" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="27" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="27" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="27" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="27" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="27" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="28" t="s">
+      <c r="C11" s="27" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="28">
+      <c r="A14" s="27">
         <v>1</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="28" t="s">
+      <c r="C14" s="27" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="28">
+      <c r="A15" s="27">
         <v>2</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="28" t="s">
+      <c r="C15" s="27" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="28">
+      <c r="A16" s="27">
         <v>3</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="27" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="28">
+      <c r="A17" s="27">
         <v>4</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="27" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="28">
+      <c r="A18" s="27">
         <v>5</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="27" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="28">
+      <c r="A19" s="27">
         <v>6</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="28" t="s">
+      <c r="C19" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="28">
+      <c r="A20" s="27">
         <v>7</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="C20" s="27" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="28">
+      <c r="A21" s="27">
         <v>8</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C21" s="28" t="s">
+      <c r="C21" s="27" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="28">
+      <c r="A22" s="27">
         <v>9</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="28" t="s">
+      <c r="C22" s="27" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="28">
+      <c r="A23" s="27">
         <v>10</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="27" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="28">
+      <c r="A24" s="27">
         <v>11</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="27" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="28">
+      <c r="A25" s="27">
         <v>12</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="28" t="s">
+      <c r="C25" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="28">
+      <c r="A26" s="27">
         <v>13</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="28" t="s">
+      <c r="C26" s="27" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="28">
+      <c r="A27" s="27">
         <v>14</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="27" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="28">
+      <c r="A28" s="27">
         <v>15</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="27" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="28">
+      <c r="A29" s="27">
         <v>16</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="28" t="s">
+      <c r="C29" s="27" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="28">
+      <c r="A30" s="27">
         <v>17</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C30" s="28" t="s">
+      <c r="C30" s="27" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="28">
+      <c r="A31" s="27">
         <v>18</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C31" s="28" t="s">
+      <c r="C31" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="28">
+      <c r="A32" s="27">
         <v>19</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="29" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="28">
+      <c r="A33" s="27">
         <v>20</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="27" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="28">
+      <c r="A34" s="27">
         <v>21</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="28" t="s">
+      <c r="C34" s="27" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="28">
+      <c r="A35" s="27">
         <v>22</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C35" s="27" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:3" s="30" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="28">
+    <row r="36" spans="1:3" s="29" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="27">
         <v>23</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C36" s="28" t="s">
+      <c r="C36" s="27" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="28" t="s">
+      <c r="A45" s="27" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="27" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="27" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="27" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="27" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="28">
+      <c r="A50" s="27">
         <v>1</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="27" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="28">
+      <c r="A51" s="27">
         <v>2</v>
       </c>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="27" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="28">
+      <c r="A52" s="27">
         <v>3</v>
       </c>
-      <c r="B52" s="28" t="s">
+      <c r="B52" s="27" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="28">
+      <c r="A53" s="27">
         <v>4</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="27" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="28">
+      <c r="A54" s="27">
         <v>5</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="27" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="28">
+      <c r="A55" s="27">
         <v>6</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="27" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="28" t="s">
+      <c r="A56" s="27" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B58" s="28" t="s">
+      <c r="B58" s="27" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="27" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="27" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="27" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="27" t="s">
         <v>77</v>
       </c>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="32"/>
+      <c r="D62" s="30"/>
+      <c r="E62" s="30"/>
+      <c r="F62" s="30"/>
+      <c r="G62" s="31"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B63" s="28" t="s">
+      <c r="B63" s="27" t="s">
         <v>76</v>
       </c>
-      <c r="C63" s="31"/>
-      <c r="D63" s="31"/>
-      <c r="E63" s="31"/>
-      <c r="F63" s="31"/>
-      <c r="G63" s="32"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="30"/>
+      <c r="E63" s="30"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="31"/>
     </row>
     <row r="64" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="31"/>
-      <c r="C64" s="31"/>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" s="28" t="s">
+      <c r="A65" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="B65" s="31"/>
-      <c r="C65" s="32" t="s">
+      <c r="B65" s="30"/>
+      <c r="C65" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="D65" s="32"/>
-      <c r="E65" s="32"/>
-      <c r="F65" s="32"/>
-      <c r="G65" s="32"/>
+      <c r="D65" s="31"/>
+      <c r="E65" s="31"/>
+      <c r="F65" s="31"/>
+      <c r="G65" s="31"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B66" s="31"/>
-      <c r="C66" s="32"/>
-      <c r="D66" s="32"/>
-      <c r="E66" s="32"/>
-      <c r="F66" s="32"/>
-      <c r="G66" s="32"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
     </row>
     <row r="67" spans="1:7" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="31" t="s">
+      <c r="B67" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C67" s="32"/>
-      <c r="D67" s="32"/>
-      <c r="E67" s="32"/>
-      <c r="F67" s="32"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B68" s="31" t="s">
+      <c r="B68" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="31">
         <v>2566</v>
       </c>
-      <c r="D68" s="32"/>
-      <c r="E68" s="32"/>
-      <c r="F68" s="32"/>
-      <c r="G68" s="31"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
+      <c r="F68" s="31"/>
+      <c r="G68" s="30"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B69" s="33" t="s">
+      <c r="B69" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="31">
         <v>2567</v>
       </c>
-      <c r="D69" s="34"/>
-      <c r="E69" s="34"/>
-      <c r="F69" s="34"/>
+      <c r="D69" s="33"/>
+      <c r="E69" s="33"/>
+      <c r="F69" s="33"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B70" s="28" t="s">
+      <c r="B70" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="C70" s="32">
+      <c r="C70" s="31">
         <v>2568</v>
       </c>
-      <c r="D70" s="34"/>
-      <c r="E70" s="34"/>
-      <c r="F70" s="34"/>
-      <c r="G70" s="33"/>
+      <c r="D70" s="33"/>
+      <c r="E70" s="33"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="32"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="C71" s="32">
+      <c r="C71" s="31">
         <v>2569</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B72" s="28" t="s">
+      <c r="B72" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="C72" s="32">
+      <c r="C72" s="31">
         <v>2570</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="19"/>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="C73" s="32">
+      <c r="C73" s="31">
         <v>2571</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B74" s="29" t="s">
+      <c r="B74" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="32">
+      <c r="C74" s="31">
         <v>2572</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B75" s="29" t="s">
+      <c r="B75" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="C75" s="32">
+      <c r="C75" s="31">
         <v>2573</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="24" x14ac:dyDescent="0.4">
-      <c r="B76" s="35" t="s">
+      <c r="B76" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="C76" s="32">
+      <c r="C76" s="31">
         <v>2574</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="24" x14ac:dyDescent="0.4">
-      <c r="B77" s="35" t="s">
+      <c r="B77" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="C77" s="32">
+      <c r="C77" s="31">
         <v>2575</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="B78" s="28" t="s">
+      <c r="B78" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="C78" s="32">
+      <c r="C78" s="31">
         <v>2576</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C79" s="32">
+      <c r="C79" s="31">
         <v>2577</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="28" t="s">
+      <c r="A81" s="27" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B83" s="28" t="s">
+      <c r="B83" s="27" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B84" s="28" t="s">
+      <c r="B84" s="27" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B85" s="28" t="s">
+      <c r="B85" s="27" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B86" s="28" t="s">
+      <c r="B86" s="27" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B87" s="28" t="s">
+      <c r="B87" s="27" t="s">
         <v>116</v>
       </c>
     </row>
@@ -3202,7 +3382,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:K653"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P653"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="3" customWidth="1"/>
@@ -3218,7 +3401,7 @@
     <col min="12" max="16384" width="10.83203125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="4"/>
@@ -3226,24 +3409,24 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="4"/>
-      <c r="H1" s="36"/>
+      <c r="H1" s="35"/>
       <c r="I1" s="20" t="s">
         <v>133</v>
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
       <c r="H2" s="19"/>
       <c r="I2" s="21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="4"/>
       <c r="B4" s="42" t="s">
         <v>0</v>
@@ -3256,21 +3439,21 @@
       <c r="H4" s="42"/>
       <c r="I4" s="42"/>
     </row>
-    <row r="5" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="38"/>
-      <c r="B5" s="39" t="s">
+    <row r="5" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="37"/>
+      <c r="B5" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="38"/>
-    </row>
-    <row r="6" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="38"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="38"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="37"/>
+    </row>
+    <row r="6" spans="1:15" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4"/>
       <c r="B6" s="22" t="s">
         <v>117</v>
@@ -3283,7 +3466,7 @@
       <c r="H6" s="18"/>
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4"/>
       <c r="B7" s="19" t="s">
         <v>127</v>
@@ -3296,10 +3479,10 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
     </row>
-    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="9"/>
       <c r="B9" s="19" t="s">
         <v>134</v>
@@ -3308,7 +3491,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="9"/>
       <c r="C10" s="4" t="s">
         <v>125</v>
@@ -3320,7 +3503,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="9"/>
       <c r="B11" s="20" t="s">
         <v>143</v>
@@ -3328,18 +3511,21 @@
       <c r="C11" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O11" s="23"/>
+    </row>
+    <row r="12" spans="1:15" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="5"/>
       <c r="C12" s="4" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O12" s="23"/>
+    </row>
+    <row r="13" spans="1:15" ht="10.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="9"/>
-    </row>
-    <row r="14" spans="1:11" ht="23" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O13" s="23"/>
+    </row>
+    <row r="14" spans="1:15" ht="23" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9"/>
       <c r="B14" s="23" t="s">
         <v>135</v>
@@ -3350,7 +3536,7 @@
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
     </row>
-    <row r="15" spans="1:11" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" ht="21.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9"/>
       <c r="B15" s="23" t="s">
         <v>144</v>
@@ -3361,9 +3547,9 @@
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
     </row>
-    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="36" t="s">
         <v>141</v>
       </c>
       <c r="C16" s="19"/>
@@ -3376,11 +3562,11 @@
       </c>
       <c r="G16" s="19"/>
     </row>
-    <row r="17" spans="1:11" ht="7.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" ht="7.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9"/>
       <c r="B17" s="8"/>
     </row>
-    <row r="18" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="9"/>
       <c r="B18" s="23" t="s">
         <v>85</v>
@@ -3389,28 +3575,43 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="9"/>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G19" s="5"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="9"/>
       <c r="C20" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G20" s="5"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="C21" s="4" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G21" s="5"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+      <c r="K21" s="7"/>
+    </row>
+    <row r="22" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9"/>
       <c r="B22" s="19" t="s">
         <v>129</v>
@@ -3421,7 +3622,7 @@
       <c r="E22" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="40">
         <v>2569</v>
       </c>
       <c r="G22" s="25" t="s">
@@ -3433,13 +3634,15 @@
       <c r="I22" s="24" t="s">
         <v>87</v>
       </c>
-      <c r="J22" s="41">
+      <c r="J22" s="40">
         <v>2569</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O22" s="41"/>
+      <c r="P22" s="23"/>
+    </row>
+    <row r="23" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="9"/>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>89</v>
       </c>
       <c r="C23" s="19" t="s">
@@ -3449,7 +3652,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" ht="26" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9"/>
       <c r="B24" s="5"/>
       <c r="C24" s="19" t="s">
@@ -3457,7 +3660,7 @@
       </c>
       <c r="F24" s="19"/>
     </row>
-    <row r="25" spans="1:11" ht="25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9"/>
       <c r="C25" s="19" t="s">
         <v>119</v>
@@ -3466,50 +3669,49 @@
         <v>138</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="9"/>
       <c r="C26" s="19" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="C27" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="9"/>
       <c r="B28" s="5"/>
       <c r="C28" s="19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="9"/>
       <c r="B29" s="5"/>
       <c r="C29" s="4" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="9"/>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="26" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="9"/>
       <c r="F31" s="9"/>
       <c r="J31" s="5"/>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="16.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="B32" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F32" s="9"/>
       <c r="G32" s="5"/>
       <c r="H32" s="9"/>
       <c r="I32" s="5"/>
@@ -3527,9 +3729,13 @@
       <c r="J33" s="5"/>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9"/>
+      <c r="B34" s="4" t="s">
+        <v>147</v>
+      </c>
       <c r="G34" s="5"/>
+      <c r="H34" s="9"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5"/>
       <c r="K34" s="7"/>
@@ -3568,13 +3774,13 @@
     </row>
     <row r="38" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="9"/>
-      <c r="F38" s="27" t="s">
+      <c r="F38" s="26" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9"/>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="26" t="s">
         <v>91</v>
       </c>
     </row>
@@ -4626,7 +4832,7 @@
     <mergeCell ref="C37:D37"/>
   </mergeCells>
   <pageMargins left="0.78740157480314998" right="0.59055118110236204" top="0.39370078740157499" bottom="0.39370078740157499" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="85" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>

--- a/Doc/ฟอร์มเอกสารแบบ-บ1_67130701930 DBIS.xlsx
+++ b/Doc/ฟอร์มเอกสารแบบ-บ1_67130701930 DBIS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krissanap/Document/KMUTT/Short Paper/Codesk_v2/Doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5DED67-6715-CA44-8E05-29985FE01F1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460E1199-52B8-D245-A6A3-2ADEEBAF2147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1771,23 +1771,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0">
-              <a:effectLst/>
-              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t>INT670</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" baseline="0">
-              <a:effectLst/>
-              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="th-TH" sz="1400" b="0" i="0">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -1796,12 +1780,20 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
             </a:rPr>
-            <a:t>Database Programming, Architecture and Administration Workshop</a:t>
+            <a:t>SEA670 Cloud Computing Worksho</a:t>
           </a:r>
-          <a:endParaRPr lang="en-US" sz="1400">
-            <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-            <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
-          </a:endParaRPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Angsana New" panose="02020603050405020304" pitchFamily="18" charset="-34"/>
+            </a:rPr>
+            <a:t>p</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2406,7 +2398,7 @@
         <xdr:cNvPr id="4" name="รูปภาพ 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D2BC5E7B-B042-7DBB-2F9A-423584C1D0F1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3555,7 +3547,7 @@
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
       <c r="E16" s="24" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>2</v>
@@ -3629,7 +3621,7 @@
         <v>88</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I22" s="24" t="s">
         <v>87</v>
